--- a/InFiRA-QA/688179-QA.xlsx
+++ b/InFiRA-QA/688179-QA.xlsx
@@ -98,9 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>22.66倍</t>
-  </si>
-  <si>
     <t>请按照母公司财务报表计算2021年度总营业费用率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -263,6 +260,10 @@
   </si>
   <si>
     <t>按照合并财务报表计算该公司2022年的流动比率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23.66倍</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -653,10 +654,10 @@
     </row>
     <row r="2" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -664,18 +665,18 @@
     </row>
     <row r="3" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="B4" s="5">
         <v>816700677.14999998</v>
@@ -686,7 +687,7 @@
     </row>
     <row r="5" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5">
         <v>85340942.780000001</v>
@@ -697,7 +698,7 @@
     </row>
     <row r="6" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5">
         <v>1303590.46</v>
@@ -706,12 +707,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>3</v>
@@ -719,10 +720,10 @@
     </row>
     <row r="8" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="C8" t="s">
         <v>3</v>
@@ -730,7 +731,7 @@
     </row>
     <row r="9" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="6">
         <v>0.59130000000000005</v>
@@ -741,7 +742,7 @@
     </row>
     <row r="10" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="7">
         <v>1366694.73</v>
@@ -752,7 +753,7 @@
     </row>
     <row r="11" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="5">
         <v>48</v>
@@ -763,10 +764,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="C12" t="s">
         <v>3</v>
@@ -774,10 +775,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="C13" t="s">
         <v>3</v>
@@ -785,7 +786,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B14" s="8">
         <v>570</v>
@@ -796,10 +797,10 @@
     </row>
     <row r="15" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="C15" t="s">
         <v>3</v>
@@ -807,7 +808,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" s="8">
         <v>0</v>
@@ -818,7 +819,7 @@
     </row>
     <row r="17" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="5">
         <v>100970869.69</v>
@@ -827,9 +828,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="5">
         <v>6072350.5800000001</v>
@@ -840,7 +841,7 @@
     </row>
     <row r="19" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" s="5">
         <v>449105.98</v>
@@ -851,7 +852,7 @@
     </row>
     <row r="20" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" s="5">
         <v>3636383.7</v>
@@ -860,9 +861,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" s="5">
         <v>375778000</v>
@@ -873,7 +874,7 @@
     </row>
     <row r="22" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="6">
         <v>-0.2697</v>
@@ -884,10 +885,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -895,7 +896,7 @@
     </row>
     <row r="24" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="6">
         <v>0.71789999999999998</v>
@@ -906,10 +907,10 @@
     </row>
     <row r="25" spans="1:3" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -917,18 +918,18 @@
     </row>
     <row r="26" spans="1:3" ht="28.8" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>43</v>
-      </c>
       <c r="C26" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="8">
         <v>7.23</v>
@@ -992,7 +993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>11</v>
       </c>
@@ -1063,15 +1064,15 @@
         <v>19</v>
       </c>
       <c r="B39" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C39" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="B40" s="10">
         <v>0.28149999999999997</v>
@@ -1082,10 +1083,10 @@
     </row>
     <row r="41" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>22</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>23</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
